--- a/策划文档/项目概述/项目概述.xlsx
+++ b/策划文档/项目概述/项目概述.xlsx
@@ -9,13 +9,14 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="19788" windowHeight="13380"/>
+    <workbookView windowWidth="27945" windowHeight="11805" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="log" sheetId="4" r:id="rId1"/>
-    <sheet name="整体概述" sheetId="1" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
+    <sheet name="log" sheetId="1" r:id="rId1"/>
+    <sheet name="目录" sheetId="2" r:id="rId2"/>
+    <sheet name="整体概述" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="69">
   <si>
     <t>日期</t>
   </si>
@@ -43,127 +44,218 @@
     <t>迭代内容</t>
   </si>
   <si>
-    <t>提交人</t>
+    <t>修改人</t>
   </si>
   <si>
     <t>单号</t>
   </si>
   <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
     <t>创建文档</t>
   </si>
   <si>
     <t>AW</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>2026-09-05</t>
+  </si>
+  <si>
+    <t>建立六大模块开发指南（系统_玩法 / 数值_经济 / 战斗_AI / UI_音效_资源 / 世界_关卡 / 引擎需求），明确各模块职责边界、文件落点与跨模块同步点</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>2026-09-06</t>
+  </si>
+  <si>
+    <t>补充设计稿特殊机制武器（鼠标准心 / 蓄力射击 / 发射环红弧 / 环绕六边形）与 UI 侧小地图升级为多箱庭固定视窗</t>
+  </si>
+  <si>
+    <t>2026-09-12</t>
+  </si>
+  <si>
+    <t>补充运镜编辑器与播放器、像素画板、Boss 战激活与播放运镜事件、能量门「只挡子弹」模式、子弹改为连续碰撞判定（修高速弹穿墙）</t>
+  </si>
+  <si>
+    <t>2026-09-13</t>
+  </si>
+  <si>
+    <t>补充策划表格驱动的局内商店与老虎机、局内消耗品与限时武器 HUD、玩家被击败失败流程与默认死亡运镜、武器本体环链与出场动画</t>
+  </si>
+  <si>
+    <t>2026-09-15</t>
+  </si>
+  <si>
+    <t>补充休息火堆、宝箱上锁解锁与可改尺寸、触发器每波与关卡级敌人数值三层回落、重装机兵远程激光单位</t>
+  </si>
+  <si>
+    <t>补全「三、包含模块」各模块功能点，新增「四、策划文档索引」（对应 32 份策划文档）；全表字体统一为微软雅黑</t>
+  </si>
+  <si>
+    <t>新增「目录」页：一~四章及各模块条目可点击跳转正文对应行</t>
+  </si>
+  <si>
+    <t>文档目录</t>
+  </si>
+  <si>
+    <t>一、项目类型</t>
+  </si>
+  <si>
+    <t>二、主要玩法</t>
+  </si>
+  <si>
+    <t>2.1 核心玩法</t>
+  </si>
+  <si>
+    <t>2.2 美术基调</t>
+  </si>
+  <si>
+    <t>三、包含模块</t>
+  </si>
+  <si>
+    <t>1.系统_玩法</t>
+  </si>
+  <si>
+    <t>2.数值_经济</t>
+  </si>
+  <si>
+    <t>3.战斗_AI</t>
+  </si>
+  <si>
+    <t>4.UI_音效_资源</t>
+  </si>
+  <si>
+    <t>5.世界_关卡</t>
+  </si>
+  <si>
+    <t>6.引擎需求</t>
+  </si>
+  <si>
+    <t>四、策划文档索引</t>
+  </si>
+  <si>
     <t>项目概述</t>
   </si>
   <si>
-    <t>一、项目类型</t>
-  </si>
-  <si>
     <t>俯视角Rougelike玩法，融合地牢探险、推车占点游戏元素</t>
   </si>
   <si>
     <t>核心差异化内容：针对 *射击* 本身进行开发创造，制造全新的射击体验与手感</t>
   </si>
   <si>
-    <t>二、主要玩法</t>
-  </si>
-  <si>
-    <t>2.1 核心玩法</t>
-  </si>
-  <si>
-    <r>
-      <t>采用</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>非直接瞄准</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>的设定，准心在围绕玩家始终转动，玩家要做的是点击屏幕控制火力的朝向。通过更强的火力与更低的操纵使得玩家能够专注于射击本身的乐趣，同时制造绚丽的画面体验</t>
-    </r>
-  </si>
-  <si>
-    <t>同时引入箱庭玩法、占点与推车玩法，围绕射击玩法本身 结合游戏背景叙事为玩家提供持续的正向心流</t>
-  </si>
-  <si>
-    <t>2.3 美术基调</t>
-  </si>
-  <si>
-    <t>相比于多为像素风格的箱庭类战斗游戏（以撒的结合，元气骑士），本项目采取完全相反的几何矢量构图，在任何分辨率下都不会丢失清晰度，同时内存友好</t>
-  </si>
-  <si>
-    <t>三、包含模块</t>
-  </si>
-  <si>
-    <r>
-      <t>后续迭代将按照如下模块进行推进</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（待补充）</t>
-    </r>
-  </si>
-  <si>
-    <t>1.系统_玩法</t>
-  </si>
-  <si>
-    <t>箱庭地牢闯关</t>
-  </si>
-  <si>
-    <t>移动运载目标（推车）</t>
-  </si>
-  <si>
-    <t>占领目标（占点）</t>
-  </si>
-  <si>
-    <t>2.数值_经济</t>
-  </si>
-  <si>
-    <t>3.战斗_AI</t>
-  </si>
-  <si>
-    <t>4.UI_音效_资源</t>
-  </si>
-  <si>
-    <t>5.世界_关卡</t>
-  </si>
-  <si>
-    <t>6.引擎需求</t>
+    <t>采用非直接瞄准的设定，准心在围绕玩家始终转动，玩家要做的是点击屏幕控制火力的朝向。</t>
+  </si>
+  <si>
+    <t>通过更强的火力与更低的操纵使得玩家能够专注于射击本身的乐趣，同时制造绚丽的画面体验。</t>
+  </si>
+  <si>
+    <t>同时引入箱庭玩法、占点与推车玩法，围绕射击玩法本身结合游戏背景叙事为玩家提供持续的正向心流。</t>
+  </si>
+  <si>
+    <t>相比于多为像素风格的箱庭类战斗游戏（以撒的结合，元气骑士），本项目采取完全相反的几何矢量构图，在任何分辨率下都不会丢失清晰度，同时内存友好。</t>
+  </si>
+  <si>
+    <t>后续迭代将按照如下模块进行推进（已补充各模块功能点，见下）</t>
+  </si>
+  <si>
+    <t>箱庭地牢闯关 / 移动运载目标（推车） / 占领目标（占点） / 登录与存档选择 / 新手引导 / 骑士之家 / 工坊装备与加点</t>
+  </si>
+  <si>
+    <t>伤害与属性公式 / 掉落与拾取经济 / 物品与改件数值 / 加点与存档成长 / 局内商店与老虎机 / 局内消耗品与限时武器 / 休息火堆与武器祝福</t>
+  </si>
+  <si>
+    <t>武器与弹道 / 敌人AI与行为（含重装机兵） / BOSS 原型机-2-5T5 / 伤害命中与护盾 / 可破坏物与宠物</t>
+  </si>
+  <si>
+    <t>战斗 HUD / 局内消耗品 HUD 与药水轮盘 / 全屏弹窗页与结算 / 世界层渲染与敌人美术 / data/ui 节点图与点击派发</t>
+  </si>
+  <si>
+    <t>关卡结构与房间 / 触发器与敌人波次 / 刷怪点与可达性 / 关卡交互物 / 关卡流程与死亡运镜</t>
+  </si>
+  <si>
+    <t>编辑器交互与撤销 / 实体属性面板 / 相机与运镜 / 落盘与 Server API / 画板与美术资产 / 武器宠物编辑器与导表打包</t>
+  </si>
+  <si>
+    <t>各模块的策划需求文档统一按「分类名_功能_需求.xlsx」命名放在下列目录，每份含编辑列表、目录与正文（系统说明 / 玩法说明）。</t>
+  </si>
+  <si>
+    <t>模块</t>
+  </si>
+  <si>
+    <t>策划文档目录</t>
+  </si>
+  <si>
+    <t>份数</t>
+  </si>
+  <si>
+    <t>策划文档清单</t>
+  </si>
+  <si>
+    <t>策划文档/系统_玩法/</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>登录与存档选择、新手引导、骑士之家、工坊装备与加点</t>
+  </si>
+  <si>
+    <t>策划文档/数值_经济/</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>伤害与属性公式、掉落与拾取经济、物品与改件数值、加点与存档成长、局内商店与老虎机、局内消耗品与限时武器、休息火堆与武器祝福</t>
+  </si>
+  <si>
+    <t>策划文档/战斗_AI/</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>武器与弹道、敌人AI与行为、BOSS原型机2-5T5、伤害命中与护盾、可破坏物与宠物</t>
+  </si>
+  <si>
+    <t>策划文档/UI_GUI/</t>
+  </si>
+  <si>
+    <t>战斗HUD、局内消耗品HUD与药水轮盘、全屏弹窗页与结算、世界层渲染与敌人美术、dataUI节点图与点击派发</t>
+  </si>
+  <si>
+    <t>策划文档/关卡_世界/</t>
+  </si>
+  <si>
+    <t>关卡结构与房间、触发器与敌人波次、刷怪点与可达性、关卡交互物、关卡流程与死亡运镜</t>
+  </si>
+  <si>
+    <t>策划文档/引擎需求/</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>编辑器交互与撤销、实体属性面板、相机与运镜、落盘与serverAPI、画板与美术资产、武器宠物编辑器与导表打包</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -174,20 +266,54 @@
     <font>
       <b/>
       <sz val="16"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF0000FF"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -335,15 +461,8 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="35">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -364,138 +483,162 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2BA02"/>
+        <bgColor rgb="FFF2BA02"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E5B3"/>
+        <bgColor rgb="FFC8E5B3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAE3F5"/>
+        <bgColor rgb="FFDAE3F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -549,53 +692,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -716,137 +818,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="36" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -856,29 +958,39 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1191,60 +1303,154 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:F5"/>
-  <sheetFormatPr defaultColWidth="15.1111111111111" defaultRowHeight="22" customHeight="1" outlineLevelRow="4" outlineLevelCol="5"/>
+  <dimension ref="B2:F10"/>
+  <sheetFormatPr defaultColWidth="15.1083333333333" defaultRowHeight="22" customHeight="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="16384" width="15.1111111111111" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6" style="2" customWidth="1"/>
+    <col min="2" max="2" width="22" style="3" customWidth="1"/>
+    <col min="3" max="3" width="62" style="3" customWidth="1"/>
+    <col min="4" max="4" width="24" style="3" customWidth="1"/>
+    <col min="5" max="6" width="12" style="3" customWidth="1"/>
+    <col min="7" max="16384" width="6" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" customHeight="1" spans="2:6">
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="10" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="2:6">
-      <c r="B3" s="10">
-        <v>46244</v>
-      </c>
-      <c r="C3" s="8" t="s">
+      <c r="B3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="7"/>
+      <c r="E3" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="4" customHeight="1" spans="2:6">
-      <c r="B4" s="7"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
+      <c r="B4" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="5" customHeight="1" spans="2:6">
-      <c r="B5" s="7"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
+      <c r="B5" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="2:6">
+      <c r="B6" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="2:6">
+      <c r="B7" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="2:6">
+      <c r="B8" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="2:6">
+      <c r="B9" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="2:6">
+      <c r="B10" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="9">
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1254,135 +1460,100 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="24" customHeight="1" outlineLevelCol="4"/>
+  <dimension ref="B1:E13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="6" style="3" customWidth="1"/>
+    <col min="2" max="2" width="26" style="3" customWidth="1"/>
+    <col min="3" max="3" width="44" style="3" customWidth="1"/>
+    <col min="4" max="4" width="12" style="3" customWidth="1"/>
+    <col min="5" max="5" width="42" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:5">
-      <c r="A1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-    </row>
-    <row r="2" customHeight="1" spans="1:5">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A4" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="1:5">
-      <c r="B6" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="1:5">
-      <c r="B7" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:5">
-      <c r="A9" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="1:5">
-      <c r="B11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="6"/>
-    </row>
-    <row r="12" customHeight="1" spans="1:5">
+    <row r="1" ht="24" customHeight="1" spans="2:3">
+      <c r="B1" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" ht="18" spans="2:3">
+      <c r="B2" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" ht="18" spans="2:3">
+      <c r="B3" s="13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" ht="16.5" spans="2:3">
+      <c r="C4" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" ht="16.5" spans="2:3">
+      <c r="C5" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" ht="18" spans="2:3">
+      <c r="B6" s="13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" spans="2:3">
+      <c r="C7" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" spans="2:3">
+      <c r="C8" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" spans="2:3">
+      <c r="C9" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="2:3">
+      <c r="C10" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="2:3">
+      <c r="C11" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" spans="2:3">
       <c r="C12" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="1:5">
-      <c r="C13" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="1:5">
-      <c r="B16" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="1:3">
-      <c r="C17" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:3">
-      <c r="A24" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="1:3">
-      <c r="B26" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="1:3">
-      <c r="B27" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="1:3">
-      <c r="C28" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="1:3">
-      <c r="C29" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="1:3">
-      <c r="C30" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="1:3">
-      <c r="B31" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="1:3">
-      <c r="B32" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="2:2">
-      <c r="B33" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="2:2">
-      <c r="B34" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="2:2">
-      <c r="B35" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" ht="18" spans="2:3">
+      <c r="B13" s="13" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E2"/>
+    <mergeCell ref="B1:E1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" display="一、项目类型"/>
+    <hyperlink ref="B3" r:id="rId2" display="二、主要玩法"/>
+    <hyperlink ref="C4" r:id="rId3" display="2.1 核心玩法"/>
+    <hyperlink ref="C5" r:id="rId4" display="2.2 美术基调"/>
+    <hyperlink ref="B6" r:id="rId5" display="三、包含模块"/>
+    <hyperlink ref="C7" r:id="rId6" display="1.系统_玩法"/>
+    <hyperlink ref="C8" r:id="rId7" display="2.数值_经济"/>
+    <hyperlink ref="C9" r:id="rId8" display="3.战斗_AI"/>
+    <hyperlink ref="C10" r:id="rId9" display="4.UI_音效_资源"/>
+    <hyperlink ref="C11" r:id="rId10" display="5.世界_关卡"/>
+    <hyperlink ref="C12" r:id="rId11" display="6.引擎需求"/>
+    <hyperlink ref="B13" r:id="rId12" display="四、策划文档索引"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -1390,9 +1561,263 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
-  <sheetData/>
+  <dimension ref="A1:E47"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="24" customHeight="1" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="6" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26" style="3" customWidth="1"/>
+    <col min="3" max="3" width="44" style="3" customWidth="1"/>
+    <col min="4" max="4" width="10" style="3" customWidth="1"/>
+    <col min="5" max="5" width="42" style="3" customWidth="1"/>
+    <col min="6" max="16384" width="6" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" spans="1:3">
+      <c r="A1" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" ht="13.5"/>
+    <row r="4" s="1" customFormat="1" ht="18" spans="1:3">
+      <c r="A4" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" ht="33" spans="1:3">
+      <c r="B6" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" ht="49.5" spans="1:3">
+      <c r="B7" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="18" spans="1:3">
+      <c r="A9" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" ht="15" spans="1:3">
+      <c r="B11" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" ht="33" spans="1:3">
+      <c r="C12" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" ht="33" spans="1:3">
+      <c r="C13" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" ht="33" spans="1:3">
+      <c r="C14" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" ht="15" spans="1:3">
+      <c r="B16" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" ht="66" spans="1:3">
+      <c r="C17" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" ht="18" spans="1:3">
+      <c r="A19" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" ht="49.5" spans="1:3">
+      <c r="B21" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" ht="15" spans="1:3">
+      <c r="B22" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" ht="66" spans="1:3">
+      <c r="B23" s="9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="15" spans="1:3">
+      <c r="B24" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" ht="82.5" spans="1:3">
+      <c r="B25" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" ht="15" spans="1:3">
+      <c r="B26" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" ht="66" spans="1:3">
+      <c r="B27" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="28" ht="15" spans="1:3">
+      <c r="B28" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" ht="66" spans="1:3">
+      <c r="B29" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" ht="15" spans="1:3">
+      <c r="B30" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" ht="66" spans="1:3">
+      <c r="B31" s="9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="32" ht="15" spans="1:3">
+      <c r="B32" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" ht="66" spans="1:5">
+      <c r="B33" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="34" ht="13.5"/>
+    <row r="35" ht="18" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" ht="82.5" spans="1:5">
+      <c r="B37" s="9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="39" ht="15" spans="1:5">
+      <c r="B39" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="40" ht="33" spans="1:5">
+      <c r="B40" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="41" ht="49.5" spans="1:5">
+      <c r="B41" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="42" ht="33" spans="1:5">
+      <c r="B42" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="43" ht="49.5" spans="1:5">
+      <c r="B43" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="44" ht="33" spans="1:5">
+      <c r="B44" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="45" ht="49.5" spans="1:5">
+      <c r="B45" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="47" ht="16.5" spans="1:5">
+      <c r="B47" s="9"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A1:E2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -1403,7 +1828,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
